--- a/data/mold-data.xlsx
+++ b/data/mold-data.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="452">
   <si>
     <t>内部ID</t>
   </si>
@@ -93,802 +93,952 @@
     <t>其他备注</t>
   </si>
   <si>
+    <t>螺mr4co1ldd0aau</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2.6  x 12</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>26B</t>
+  </si>
+  <si>
+    <t>B束尾</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld3qhhb</t>
+  </si>
+  <si>
+    <t>2 x 8</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>20P</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldkj2sz</t>
+  </si>
+  <si>
+    <t>2 x 5</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldpscca</t>
+  </si>
+  <si>
+    <t>2.5 X 10</t>
+  </si>
+  <si>
+    <t>26P</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>1.6+0.1</t>
+  </si>
+  <si>
+    <t>9.4</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldx7iit</t>
+  </si>
+  <si>
+    <t>2.5 X 6</t>
+  </si>
+  <si>
+    <t>4.1+1</t>
+  </si>
+  <si>
+    <t>1.6+1</t>
+  </si>
+  <si>
+    <t>5.6+0.1</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldr6lo5</t>
+  </si>
+  <si>
+    <t>3 X10</t>
+  </si>
+  <si>
+    <t>DIN 7985</t>
+  </si>
+  <si>
+    <t>7985 M3 M=2.8</t>
+  </si>
+  <si>
+    <t>5.3 ±0.1</t>
+  </si>
+  <si>
+    <t>2.3±0.1</t>
+  </si>
+  <si>
+    <t>10-0.3</t>
+  </si>
+  <si>
+    <t>9.1±0.1</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldc5dq8</t>
+  </si>
+  <si>
+    <t>2.5 X 23</t>
+  </si>
+  <si>
+    <t>7985 M3</t>
+  </si>
+  <si>
+    <t>4.9~5.1</t>
+  </si>
+  <si>
+    <t>1.9-2.0</t>
+  </si>
+  <si>
+    <t>23±0.5</t>
+  </si>
+  <si>
+    <t>2.5~2.6</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld4n5dj</t>
+  </si>
+  <si>
+    <t>5.5 X 13</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>60T D=14.5</t>
+  </si>
+  <si>
+    <t>11-0.43</t>
+  </si>
+  <si>
+    <t>3.6-4</t>
+  </si>
+  <si>
+    <t>13±0.8</t>
+  </si>
+  <si>
+    <t>5.4~5.6</t>
+  </si>
+  <si>
+    <t>4.38</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldch8ic</t>
+  </si>
+  <si>
+    <t>3 X 8</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>30R</t>
+  </si>
+  <si>
+    <t>5.3~5.4</t>
+  </si>
+  <si>
+    <t>8.0-0.5</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld0feq0</t>
+  </si>
+  <si>
+    <t>2.5 X 8</t>
+  </si>
+  <si>
+    <t>4.05~4.2</t>
+  </si>
+  <si>
+    <t>1.6~2.0</t>
+  </si>
+  <si>
+    <t>2.4~2.6</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld6v7ol</t>
+  </si>
+  <si>
+    <t>3 X 10</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>30F</t>
+  </si>
+  <si>
+    <t>2.28</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldvty40</t>
+  </si>
+  <si>
+    <t>4.2 X 16</t>
+  </si>
+  <si>
+    <t>SNK 138 D=6.7</t>
+  </si>
+  <si>
+    <t>2.88</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldr3w9f</t>
+  </si>
+  <si>
+    <t>4.8 X 25</t>
+  </si>
+  <si>
+    <t>50B</t>
+  </si>
+  <si>
+    <t>3.68</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldkd2rw</t>
+  </si>
+  <si>
+    <t>4.8 X 18</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldhcbkn</t>
+  </si>
+  <si>
+    <t>5 X 16</t>
+  </si>
+  <si>
+    <t>梅花带柱</t>
+  </si>
+  <si>
+    <t>7380 M5 T25 孔1.4</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>4.34 10B21</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld8v7re</t>
+  </si>
+  <si>
+    <t>4 X 6</t>
+  </si>
+  <si>
+    <t>40T</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>3.43</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldy9f5y</t>
+  </si>
+  <si>
+    <t>4.2 X 15</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>W=12-0.5</t>
+  </si>
+  <si>
+    <t>介 0.8±0.1</t>
+  </si>
+  <si>
+    <t>15-0.8</t>
+  </si>
+  <si>
+    <t>4.15~4.26</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldqzp6u</t>
+  </si>
+  <si>
+    <t>4.2 X 10</t>
+  </si>
+  <si>
+    <t>10-0.5</t>
+  </si>
+  <si>
+    <t>1.6±0.15</t>
+  </si>
+  <si>
+    <t>10±0.8</t>
+  </si>
+  <si>
+    <t>4.22-0.18</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldly19y</t>
+  </si>
+  <si>
+    <t>4.2 X 12</t>
+  </si>
+  <si>
+    <t>8.2±0.5</t>
+  </si>
+  <si>
+    <t>12+1.5</t>
+  </si>
+  <si>
+    <t>4.05~4.22</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld62d01</t>
+  </si>
+  <si>
+    <t>4.2 X 13</t>
+  </si>
+  <si>
+    <t>45P</t>
+  </si>
+  <si>
+    <t>W=9.2±0.8</t>
+  </si>
+  <si>
+    <t>11±0.1</t>
+  </si>
+  <si>
+    <t>3.31</t>
+  </si>
+  <si>
+    <t>长度尽量不正公差</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldb5sbv</t>
+  </si>
+  <si>
+    <t>45T</t>
+  </si>
+  <si>
+    <t>13-0.8</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldfv9c7</t>
+  </si>
+  <si>
+    <t>2.9 X 16</t>
+  </si>
+  <si>
+    <t>5.3~5.6</t>
+  </si>
+  <si>
+    <t>2.15~2.4</t>
+  </si>
+  <si>
+    <t>16-0.8</t>
+  </si>
+  <si>
+    <t>2.9-0.14</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld8a4hi</t>
+  </si>
+  <si>
+    <t>4 X 8</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>7±0.3</t>
+  </si>
+  <si>
+    <t>1.5±0.15</t>
+  </si>
+  <si>
+    <t>7.7~8.1</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldx9qt1</t>
+  </si>
+  <si>
+    <t>RW T20</t>
+  </si>
+  <si>
+    <t>T20 R D=6.6</t>
+  </si>
+  <si>
+    <t>8.3-0.3</t>
+  </si>
+  <si>
+    <t>介厚1</t>
+  </si>
+  <si>
+    <t>13-0.2</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldahope</t>
+  </si>
+  <si>
+    <t>4 X 22</t>
+  </si>
+  <si>
+    <t>M半牙</t>
+  </si>
+  <si>
+    <t>9.6-0.4</t>
+  </si>
+  <si>
+    <t>22-0.2 牙10</t>
+  </si>
+  <si>
+    <t>3.43 10B21</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldorht4</t>
+  </si>
+  <si>
+    <t>3 X 6</t>
+  </si>
+  <si>
+    <t>RW T10</t>
+  </si>
+  <si>
+    <t>T10 R D=5.5</t>
+  </si>
+  <si>
+    <t>7.3-0.4</t>
+  </si>
+  <si>
+    <t>6-0.2</t>
+  </si>
+  <si>
+    <t>2.6 10B21</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld20f4o</t>
+  </si>
+  <si>
+    <t>2.2 X 8</t>
+  </si>
+  <si>
+    <t>20F</t>
+  </si>
+  <si>
+    <t>3.65±0.2</t>
+  </si>
+  <si>
+    <t>8±0.5</t>
+  </si>
+  <si>
+    <t>1.95+0.1</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldcnoum</t>
+  </si>
+  <si>
+    <t>V 101 3.5 X 40.5</t>
+  </si>
+  <si>
+    <t>V 字</t>
+  </si>
+  <si>
+    <t>40.5±0.05</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>3.47</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldiulqo</t>
+  </si>
+  <si>
+    <t>V 1 3.5 X 46</t>
+  </si>
+  <si>
+    <t>46.0-0.1</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldjfzxh</t>
+  </si>
+  <si>
+    <t>D 932 3.5 X 44.4</t>
+  </si>
+  <si>
+    <t>D 字</t>
+  </si>
+  <si>
+    <t>9+0.35</t>
+  </si>
+  <si>
+    <t>44.4+0.1</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldbeli3</t>
+  </si>
+  <si>
+    <t>6390 3.5 X 38</t>
+  </si>
+  <si>
+    <t>9.1~9.3</t>
+  </si>
+  <si>
+    <t>38-0.1</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld6hxot</t>
+  </si>
+  <si>
+    <t>913 3.8 X 34.4</t>
+  </si>
+  <si>
+    <t>9.2~9.3</t>
+  </si>
+  <si>
+    <t>2.3~2.4</t>
+  </si>
+  <si>
+    <t>34.4+0.1</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>3.77</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldpmxue</t>
+  </si>
+  <si>
+    <t>N 1 3.5 X 46</t>
+  </si>
+  <si>
+    <t>45.7±0.05</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldyopee</t>
+  </si>
+  <si>
+    <t>P620 3.2 X 43.5</t>
+  </si>
+  <si>
+    <t>9.3~9.4</t>
+  </si>
+  <si>
+    <t>43.5±0.05</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldkffrz</t>
+  </si>
+  <si>
+    <t>2.6 X 8</t>
+  </si>
+  <si>
+    <t>4.5-0.5</t>
+  </si>
+  <si>
+    <t>1.7±0.2</t>
+  </si>
+  <si>
+    <t>2.4~2.7</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld83dc9</t>
+  </si>
+  <si>
+    <t>5.2±0.3</t>
+  </si>
+  <si>
+    <t>1.9±0.2</t>
+  </si>
+  <si>
+    <t>3.0±0.15</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld84w6z</t>
+  </si>
+  <si>
+    <t>3.5 X 13</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>30B 包边</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldm4rrx</t>
+  </si>
+  <si>
+    <t>4.8 X 13</t>
+  </si>
+  <si>
+    <t>50P</t>
+  </si>
+  <si>
+    <t>11.7±0.5</t>
+  </si>
+  <si>
+    <t>3.6±0.3</t>
+  </si>
+  <si>
+    <t>13±0.5</t>
+  </si>
+  <si>
+    <t>4.9±0.2</t>
+  </si>
+  <si>
+    <t>螺mr4co1ldpyuit</t>
+  </si>
+  <si>
+    <t>束尾</t>
+  </si>
+  <si>
+    <t>11.5~12</t>
+  </si>
+  <si>
+    <t>介 1.0-0.3</t>
+  </si>
+  <si>
+    <t>螺mr4co1ld5hqut</t>
+  </si>
+  <si>
+    <t>4.8 X16</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>规格</t>
+  </si>
+  <si>
+    <t>材质</t>
+  </si>
+  <si>
+    <t>安全库存</t>
+  </si>
+  <si>
+    <t>冲mr4co1letyvg7</t>
+  </si>
+  <si>
+    <t>/*</t>
+  </si>
+  <si>
+    <t>冲mr4co1le1ssam</t>
+  </si>
+  <si>
+    <t>冲mr4co1lecr2d3</t>
+  </si>
+  <si>
+    <t>冲mr4co1lezy22x</t>
+  </si>
+  <si>
+    <t>冲mr4co1leciqu7</t>
+  </si>
+  <si>
+    <t>JMB M26</t>
+  </si>
+  <si>
+    <t>冲mr4co1le8fj29</t>
+  </si>
+  <si>
+    <t>JMB M30 包边</t>
+  </si>
+  <si>
+    <t>冲mr4co1leltla1</t>
+  </si>
+  <si>
+    <t>JMB M50</t>
+  </si>
+  <si>
+    <t>冲mr4co1lecel08</t>
+  </si>
+  <si>
+    <t>JMF M20</t>
+  </si>
+  <si>
+    <t>冲mr4co1letetxb</t>
+  </si>
+  <si>
+    <t>JMF M30</t>
+  </si>
+  <si>
+    <t>冲mr4co1le6yad6</t>
+  </si>
+  <si>
+    <t>JMP M20</t>
+  </si>
+  <si>
+    <t>冲mr4co1ledgo5s</t>
+  </si>
+  <si>
+    <t>JMP M26</t>
+  </si>
+  <si>
+    <t>冲mr4co1letb8wb</t>
+  </si>
+  <si>
+    <t>JMP M45</t>
+  </si>
+  <si>
+    <t>冲mr4co1le4t7a5</t>
+  </si>
+  <si>
+    <t>JMP M50</t>
+  </si>
+  <si>
+    <t>冲mr4co1lem21cw</t>
+  </si>
+  <si>
+    <t>JMR M30</t>
+  </si>
+  <si>
+    <t>冲mr4co1leb0fk8</t>
+  </si>
+  <si>
+    <t>JMT M40</t>
+  </si>
+  <si>
+    <t>冲mr4co1lehfgjo</t>
+  </si>
+  <si>
+    <t>JMT M45</t>
+  </si>
+  <si>
+    <t>冲mr4co1lecn7ds</t>
+  </si>
+  <si>
+    <t>JMT M60 D=14.5</t>
+  </si>
+  <si>
+    <t>冲mr4co1lec00ki</t>
+  </si>
+  <si>
+    <t>冲mr4co1le23nne</t>
+  </si>
+  <si>
+    <t>冲mr4co1leor4bd</t>
+  </si>
+  <si>
+    <t>冲mr4co1lerz762</t>
+  </si>
+  <si>
+    <t>订购ID</t>
+  </si>
+  <si>
+    <t>冲头ID</t>
+  </si>
+  <si>
+    <t>订购数量</t>
+  </si>
+  <si>
+    <t>订购时间</t>
+  </si>
+  <si>
+    <t>到货状态</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>PO000001</t>
+  </si>
+  <si>
+    <t>P0011</t>
+  </si>
+  <si>
+    <t>1900-01-11</t>
+  </si>
+  <si>
+    <t>已到货</t>
+  </si>
+  <si>
+    <t>PO000002</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>PO000003</t>
+  </si>
+  <si>
+    <t>P0013</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>PO_mqxhg2mf553kc</t>
+  </si>
+  <si>
+    <t>P0003</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>未到货</t>
+  </si>
+  <si>
+    <t>领用ID</t>
+  </si>
+  <si>
+    <t>领用人</t>
+  </si>
+  <si>
+    <t>领用数量</t>
+  </si>
+  <si>
+    <t>领用时间</t>
+  </si>
+  <si>
+    <t>关联ID</t>
+  </si>
+  <si>
+    <t>螺丝规格ID</t>
+  </si>
+  <si>
+    <t>PL_mqxhgtk27wcz4</t>
+  </si>
+  <si>
+    <t>P0002</t>
+  </si>
+  <si>
     <t>SS0001</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>2.6  x 12</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>30F</t>
-  </si>
-  <si>
-    <t>B束尾</t>
+    <t>当前库存</t>
+  </si>
+  <si>
+    <t>库存状态</t>
+  </si>
+  <si>
+    <t>P0001</t>
+  </si>
+  <si>
+    <t>安全</t>
+  </si>
+  <si>
+    <t>P0004</t>
+  </si>
+  <si>
+    <t>P0005</t>
+  </si>
+  <si>
+    <t>P0006</t>
+  </si>
+  <si>
+    <t>P0007</t>
+  </si>
+  <si>
+    <t>P0008</t>
+  </si>
+  <si>
+    <t>P0009</t>
+  </si>
+  <si>
+    <t>P0010</t>
+  </si>
+  <si>
+    <t>40P</t>
+  </si>
+  <si>
+    <t>P0012</t>
+  </si>
+  <si>
+    <t>P0014</t>
+  </si>
+  <si>
+    <t>JMT 50B</t>
+  </si>
+  <si>
+    <t>P0015</t>
+  </si>
+  <si>
+    <t>P0016</t>
+  </si>
+  <si>
+    <t>60T</t>
+  </si>
+  <si>
+    <t>P0017</t>
+  </si>
+  <si>
+    <t>P0018</t>
+  </si>
+  <si>
+    <t>机型</t>
+  </si>
+  <si>
+    <t>线径</t>
+  </si>
+  <si>
+    <t>D0001</t>
+  </si>
+  <si>
+    <t>#10-13B</t>
+  </si>
+  <si>
+    <t>D0002</t>
   </si>
   <si>
     <t>M1.7-48*6</t>
-  </si>
-  <si>
-    <t>SS0002</t>
-  </si>
-  <si>
-    <t>2 x 8</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>20P</t>
-  </si>
-  <si>
-    <t>SS0003</t>
-  </si>
-  <si>
-    <t>2 x 5</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>SS0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5 X 10 </t>
-  </si>
-  <si>
-    <t>26P</t>
-  </si>
-  <si>
-    <t>1.6+0.1</t>
-  </si>
-  <si>
-    <t>SS0005</t>
-  </si>
-  <si>
-    <t>2.5 X 6</t>
-  </si>
-  <si>
-    <t>4.1+1</t>
-  </si>
-  <si>
-    <t>1.6+1</t>
-  </si>
-  <si>
-    <t>5.6+0.1</t>
-  </si>
-  <si>
-    <t>SS0006</t>
-  </si>
-  <si>
-    <t>3 X10</t>
-  </si>
-  <si>
-    <t>DIN 7985</t>
-  </si>
-  <si>
-    <t>7985 M3 M=2.8</t>
-  </si>
-  <si>
-    <t>5.3 ±0.1</t>
-  </si>
-  <si>
-    <t>2.3±0.1</t>
-  </si>
-  <si>
-    <t>10-0.3</t>
-  </si>
-  <si>
-    <t>9.1±0.1</t>
-  </si>
-  <si>
-    <t>SS0007</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.5 X 23</t>
-  </si>
-  <si>
-    <t>7985 M3</t>
-  </si>
-  <si>
-    <t>4.9~5.1</t>
-  </si>
-  <si>
-    <t>1.9-2.0</t>
-  </si>
-  <si>
-    <t>23±0.5</t>
-  </si>
-  <si>
-    <t>2.5~2.6</t>
-  </si>
-  <si>
-    <t>SS0008</t>
-  </si>
-  <si>
-    <t>5.5 X 13</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>60T D=14.5</t>
-  </si>
-  <si>
-    <t>11-0.43</t>
-  </si>
-  <si>
-    <t>3.6~4</t>
-  </si>
-  <si>
-    <t>13±0.8</t>
-  </si>
-  <si>
-    <t>5.4~5.6</t>
-  </si>
-  <si>
-    <t>SS0009</t>
-  </si>
-  <si>
-    <t>3 X 8</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>30R</t>
-  </si>
-  <si>
-    <t>5.3~5.4</t>
-  </si>
-  <si>
-    <t>8.0-0.5</t>
-  </si>
-  <si>
-    <t>SS0010</t>
-  </si>
-  <si>
-    <t>2.5 X 8</t>
-  </si>
-  <si>
-    <t>26B</t>
-  </si>
-  <si>
-    <t>4.05~4.2</t>
-  </si>
-  <si>
-    <t>1.6~2.0</t>
-  </si>
-  <si>
-    <t>2.4~2.6</t>
-  </si>
-  <si>
-    <t>SS0011</t>
-  </si>
-  <si>
-    <t>3 X 10</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>SS0012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2 X 16 </t>
-  </si>
-  <si>
-    <t>SNK 138 D=6.7</t>
-  </si>
-  <si>
-    <t>D/WS</t>
-  </si>
-  <si>
-    <t>SS0013</t>
-  </si>
-  <si>
-    <t>4.8 X 25</t>
-  </si>
-  <si>
-    <t>50B</t>
-  </si>
-  <si>
-    <t>SS0014</t>
-  </si>
-  <si>
-    <t>4.8 X 18</t>
-  </si>
-  <si>
-    <t>SS0015</t>
-  </si>
-  <si>
-    <t>5 X 16</t>
-  </si>
-  <si>
-    <t>梅花带柱</t>
-  </si>
-  <si>
-    <t>7380 M5 T25 孔1.4</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>4.34 10B21</t>
-  </si>
-  <si>
-    <t>SS0016</t>
-  </si>
-  <si>
-    <t>4 X 6</t>
-  </si>
-  <si>
-    <t>40T</t>
-  </si>
-  <si>
-    <t>SS0017</t>
-  </si>
-  <si>
-    <t>4.2 X 15</t>
-  </si>
-  <si>
-    <t>PW</t>
-  </si>
-  <si>
-    <t>W=12-0.5</t>
-  </si>
-  <si>
-    <t>介 0.8±0.1</t>
-  </si>
-  <si>
-    <t>15-0.8</t>
-  </si>
-  <si>
-    <t>4.15~4.26</t>
-  </si>
-  <si>
-    <t>SS0018</t>
-  </si>
-  <si>
-    <t>4.2 X 10</t>
-  </si>
-  <si>
-    <t>10-0.5</t>
-  </si>
-  <si>
-    <t>1.6±0.15</t>
-  </si>
-  <si>
-    <t>10±0.8</t>
-  </si>
-  <si>
-    <t>4.22-0.18</t>
-  </si>
-  <si>
-    <t>SS0019</t>
-  </si>
-  <si>
-    <t>4.2 X 12</t>
-  </si>
-  <si>
-    <t>8.2±0.5</t>
-  </si>
-  <si>
-    <t>12+1.5</t>
-  </si>
-  <si>
-    <t>4.05~4.22</t>
-  </si>
-  <si>
-    <t>SS0020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2 X 13 </t>
-  </si>
-  <si>
-    <t>45P</t>
-  </si>
-  <si>
-    <t>W=9.2±0.8</t>
-  </si>
-  <si>
-    <t>11±0.1</t>
-  </si>
-  <si>
-    <t>长度尽量不正公差</t>
-  </si>
-  <si>
-    <t>SS0021</t>
-  </si>
-  <si>
-    <t>45T</t>
-  </si>
-  <si>
-    <t>13-0.8</t>
-  </si>
-  <si>
-    <t>SS0023</t>
-  </si>
-  <si>
-    <t>2.9 X 16</t>
-  </si>
-  <si>
-    <t>5.3~5.6</t>
-  </si>
-  <si>
-    <t>2.15~2.4</t>
-  </si>
-  <si>
-    <t>16-0.8</t>
-  </si>
-  <si>
-    <t>2.9-0.14</t>
-  </si>
-  <si>
-    <t>SS0024</t>
-  </si>
-  <si>
-    <t>4 X 8</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>7±0.3</t>
-  </si>
-  <si>
-    <t>1.5±0.15</t>
-  </si>
-  <si>
-    <t>7.7~8.1</t>
-  </si>
-  <si>
-    <t>SS0025</t>
-  </si>
-  <si>
-    <t>RW T20</t>
-  </si>
-  <si>
-    <t>T20 R D=6.6</t>
-  </si>
-  <si>
-    <t>8.3-0.3</t>
-  </si>
-  <si>
-    <t>介厚1</t>
-  </si>
-  <si>
-    <t>13-0.2</t>
-  </si>
-  <si>
-    <t>SS0026</t>
-  </si>
-  <si>
-    <t>4 X 22</t>
-  </si>
-  <si>
-    <t>M半牙</t>
-  </si>
-  <si>
-    <t>9.6-0.4</t>
-  </si>
-  <si>
-    <t>22-0.2 牙10</t>
-  </si>
-  <si>
-    <t>3.43 10B21</t>
-  </si>
-  <si>
-    <t>SS0027</t>
-  </si>
-  <si>
-    <t>3 X 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RW T10 </t>
-  </si>
-  <si>
-    <t>T10 R D=5.5</t>
-  </si>
-  <si>
-    <t>7.3-0.4</t>
-  </si>
-  <si>
-    <t>6-0.2</t>
-  </si>
-  <si>
-    <t>2.6 10B21</t>
-  </si>
-  <si>
-    <t>SS0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.2 X 8</t>
-  </si>
-  <si>
-    <t>20F</t>
-  </si>
-  <si>
-    <t>3.65±0.2</t>
-  </si>
-  <si>
-    <t>8±0.5</t>
-  </si>
-  <si>
-    <t>1.95+0.1</t>
-  </si>
-  <si>
-    <t>SS0029</t>
-  </si>
-  <si>
-    <t>V 101</t>
-  </si>
-  <si>
-    <t>3.5 X 40.5</t>
-  </si>
-  <si>
-    <t>V 字</t>
-  </si>
-  <si>
-    <t>40.5±0.05</t>
-  </si>
-  <si>
-    <t>SS0030</t>
-  </si>
-  <si>
-    <t>V 1</t>
-  </si>
-  <si>
-    <t>3.5 X 46.0</t>
-  </si>
-  <si>
-    <t>46.0-0.1</t>
-  </si>
-  <si>
-    <t>SS0031</t>
-  </si>
-  <si>
-    <t>D 932</t>
-  </si>
-  <si>
-    <t>3.5 X 44.4</t>
-  </si>
-  <si>
-    <t>D 字</t>
-  </si>
-  <si>
-    <t>9+0.35</t>
-  </si>
-  <si>
-    <t>44.4+0.1</t>
-  </si>
-  <si>
-    <t>SS0032</t>
-  </si>
-  <si>
-    <t>6390</t>
-  </si>
-  <si>
-    <t>3.5 X 38</t>
-  </si>
-  <si>
-    <t>9.1~9.3</t>
-  </si>
-  <si>
-    <t>38-0.1</t>
-  </si>
-  <si>
-    <t>SS0033</t>
-  </si>
-  <si>
-    <t>913</t>
-  </si>
-  <si>
-    <t>3.8 X 34.4</t>
-  </si>
-  <si>
-    <t>9.2~9.3</t>
-  </si>
-  <si>
-    <t>2.3~2.4</t>
-  </si>
-  <si>
-    <t>34.4+0.1</t>
-  </si>
-  <si>
-    <t>SS0034</t>
-  </si>
-  <si>
-    <t>N 1</t>
-  </si>
-  <si>
-    <t>3.5 X 46</t>
-  </si>
-  <si>
-    <t>45.7±0.05</t>
-  </si>
-  <si>
-    <t>SS0035</t>
-  </si>
-  <si>
-    <t>P620</t>
-  </si>
-  <si>
-    <t>3.2 X 43.5</t>
-  </si>
-  <si>
-    <t>9.3~9.4</t>
-  </si>
-  <si>
-    <t>43.5±0.05</t>
-  </si>
-  <si>
-    <t>SS0036</t>
-  </si>
-  <si>
-    <t>2.6 X 8</t>
-  </si>
-  <si>
-    <t>4.5-0.5</t>
-  </si>
-  <si>
-    <t>1.7±0.2</t>
-  </si>
-  <si>
-    <t>2.4~2.7</t>
-  </si>
-  <si>
-    <t>SS0037</t>
-  </si>
-  <si>
-    <t>5.2±0.3</t>
-  </si>
-  <si>
-    <t>1.9±0.2</t>
-  </si>
-  <si>
-    <t>3.0±0.15</t>
-  </si>
-  <si>
-    <t>SS0038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5 X 13 </t>
-  </si>
-  <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>30B 包边</t>
-  </si>
-  <si>
-    <t>SS0039</t>
-  </si>
-  <si>
-    <t>4.8 X 13</t>
-  </si>
-  <si>
-    <t>50P</t>
-  </si>
-  <si>
-    <t>11.7±0.5</t>
-  </si>
-  <si>
-    <t>3.6±0.3</t>
-  </si>
-  <si>
-    <t>13±0.5</t>
-  </si>
-  <si>
-    <t>4.9±0.2</t>
-  </si>
-  <si>
-    <t>SS0040</t>
-  </si>
-  <si>
-    <t>束尾</t>
-  </si>
-  <si>
-    <t>11.5~12</t>
-  </si>
-  <si>
-    <t>介 1.0-0.3</t>
-  </si>
-  <si>
-    <t>SS0041</t>
-  </si>
-  <si>
-    <t>4.8 X16</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>材质</t>
-  </si>
-  <si>
-    <t>安全库存</t>
-  </si>
-  <si>
-    <t>P0001</t>
-  </si>
-  <si>
-    <t>12*15</t>
-  </si>
-  <si>
-    <t>P0002</t>
-  </si>
-  <si>
-    <t>P0003</t>
-  </si>
-  <si>
-    <t>P0004</t>
-  </si>
-  <si>
-    <t>14*15</t>
-  </si>
-  <si>
-    <t>P0005</t>
-  </si>
-  <si>
-    <t>白冲</t>
-  </si>
-  <si>
-    <t>P0006</t>
-  </si>
-  <si>
-    <t>P0007</t>
-  </si>
-  <si>
-    <t>P0008</t>
-  </si>
-  <si>
-    <t>P0009</t>
-  </si>
-  <si>
-    <t>P0010</t>
-  </si>
-  <si>
-    <t>40P</t>
-  </si>
-  <si>
-    <t>18*18</t>
-  </si>
-  <si>
-    <t>P0011</t>
-  </si>
-  <si>
-    <t>P0012</t>
-  </si>
-  <si>
-    <t>P0013</t>
-  </si>
-  <si>
-    <t>P0014</t>
-  </si>
-  <si>
-    <t>JMT 50B</t>
-  </si>
-  <si>
-    <t>P0015</t>
-  </si>
-  <si>
-    <t>P0016</t>
-  </si>
-  <si>
-    <t>60T</t>
-  </si>
-  <si>
-    <t>P0017</t>
-  </si>
-  <si>
-    <t>P0018</t>
-  </si>
-  <si>
-    <t>订购ID</t>
-  </si>
-  <si>
-    <t>冲头ID</t>
-  </si>
-  <si>
-    <t>订购数量</t>
-  </si>
-  <si>
-    <t>订购时间</t>
-  </si>
-  <si>
-    <t>到货状态</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>PO000001</t>
-  </si>
-  <si>
-    <t>1900-01-11</t>
-  </si>
-  <si>
-    <t>已到货</t>
-  </si>
-  <si>
-    <t>PO000002</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>PO000003</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>PO_mqxhg2mf553kc</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>未到货</t>
-  </si>
-  <si>
-    <t>领用ID</t>
-  </si>
-  <si>
-    <t>领用人</t>
-  </si>
-  <si>
-    <t>领用数量</t>
-  </si>
-  <si>
-    <t>领用时间</t>
-  </si>
-  <si>
-    <t>关联ID</t>
-  </si>
-  <si>
-    <t>螺丝规格ID</t>
-  </si>
-  <si>
-    <t>PL_mqxhgtk27wcz4</t>
-  </si>
-  <si>
-    <t>当前库存</t>
-  </si>
-  <si>
-    <t>库存状态</t>
-  </si>
-  <si>
-    <t>安全</t>
-  </si>
-  <si>
-    <t>机型</t>
-  </si>
-  <si>
-    <t>线径</t>
-  </si>
-  <si>
-    <t>D0001</t>
-  </si>
-  <si>
-    <t>#10-13B</t>
-  </si>
-  <si>
-    <t>D0002</t>
   </si>
   <si>
     <t>D0003</t>
@@ -1708,19 +1858,25 @@
         <v>21</v>
       </c>
       <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="I2">
-        <v>5.3</v>
-      </c>
-      <c r="J2">
-        <v>1.6</v>
-      </c>
-      <c r="M2">
-        <v>11</v>
-      </c>
-      <c r="N2">
-        <v>2.05</v>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
       <c r="O2" t="s">
         <v>17</v>
@@ -1731,7 +1887,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1740,13 +1896,13 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -1754,17 +1910,23 @@
       <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="I3">
-        <v>3.3</v>
-      </c>
-      <c r="J3">
-        <v>1.3</v>
-      </c>
-      <c r="M3">
-        <v>7.4</v>
-      </c>
-      <c r="N3">
-        <v>1.6</v>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
       </c>
       <c r="O3" t="s">
         <v>17</v>
@@ -1775,7 +1937,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -1784,31 +1946,37 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
       <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4">
-        <v>3.3</v>
-      </c>
-      <c r="J4">
-        <v>1.3</v>
-      </c>
-      <c r="M4">
-        <v>4.5</v>
-      </c>
-      <c r="N4">
-        <v>1.6</v>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
       </c>
       <c r="O4" t="s">
         <v>17</v>
@@ -1819,7 +1987,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -1828,31 +1996,37 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="I5">
-        <v>4.1</v>
+      <c r="I5" t="s">
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5">
-        <v>9.4</v>
-      </c>
-      <c r="N5">
-        <v>1.98</v>
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>44</v>
       </c>
       <c r="O5" t="s">
         <v>17</v>
@@ -1863,7 +2037,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -1872,13 +2046,13 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>19</v>
@@ -1887,16 +2061,22 @@
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>48</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6">
-        <v>1.98</v>
+        <v>49</v>
+      </c>
+      <c r="N6" t="s">
+        <v>44</v>
       </c>
       <c r="O6" t="s">
         <v>17</v>
@@ -1907,7 +2087,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -1916,13 +2096,13 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -1931,16 +2111,22 @@
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
       </c>
       <c r="O7" t="s">
         <v>17</v>
@@ -1951,7 +2137,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -1960,13 +2146,13 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -1975,19 +2161,22 @@
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8">
-        <v>1.98</v>
+        <v>64</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
       </c>
       <c r="O8" t="s">
         <v>17</v>
@@ -1998,7 +2187,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -2007,13 +2196,13 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -2022,19 +2211,22 @@
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9">
-        <v>4.38</v>
+        <v>72</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>73</v>
       </c>
       <c r="O9" t="s">
         <v>17</v>
@@ -2045,7 +2237,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -2054,28 +2246,37 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
-      </c>
-      <c r="N10">
-        <v>2.33</v>
+        <v>79</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>80</v>
       </c>
       <c r="O10" t="s">
         <v>17</v>
@@ -2086,7 +2287,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -2095,34 +2296,37 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K11" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
-      </c>
-      <c r="N11">
-        <v>1.98</v>
+        <v>85</v>
+      </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>44</v>
       </c>
       <c r="O11" t="s">
         <v>17</v>
@@ -2133,7 +2337,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -2142,22 +2346,37 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
-      <c r="N12">
-        <v>2.28</v>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>90</v>
       </c>
       <c r="O12" t="s">
         <v>17</v>
@@ -2168,7 +2387,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -2177,22 +2396,37 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
-      <c r="N13">
-        <v>2.88</v>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>94</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
@@ -2203,7 +2437,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -2212,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G14" t="s">
         <v>19</v>
@@ -2226,8 +2460,23 @@
       <c r="H14" t="s">
         <v>17</v>
       </c>
-      <c r="N14">
-        <v>3.68</v>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>98</v>
       </c>
       <c r="O14" t="s">
         <v>17</v>
@@ -2238,7 +2487,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -2247,13 +2496,13 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
@@ -2261,8 +2510,23 @@
       <c r="H15" t="s">
         <v>17</v>
       </c>
-      <c r="N15">
-        <v>3.68</v>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>98</v>
       </c>
       <c r="O15" t="s">
         <v>17</v>
@@ -2273,7 +2537,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -2282,22 +2546,37 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
       <c r="N16" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="O16" t="s">
         <v>17</v>
@@ -2308,7 +2587,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -2317,28 +2596,37 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
-      <c r="I17">
-        <v>8.5</v>
-      </c>
-      <c r="J17">
-        <v>2.5</v>
-      </c>
-      <c r="N17">
-        <v>3.43</v>
+      <c r="I17" t="s">
+        <v>110</v>
+      </c>
+      <c r="J17" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>112</v>
       </c>
       <c r="O17" t="s">
         <v>17</v>
@@ -2349,7 +2637,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -2358,10 +2646,10 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
@@ -2373,16 +2661,22 @@
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="K18" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="L18" t="s">
-        <v>102</v>
+        <v>119</v>
+      </c>
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
       </c>
       <c r="O18" t="s">
         <v>17</v>
@@ -2393,7 +2687,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -2402,7 +2696,7 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -2417,16 +2711,22 @@
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="J19" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="L19" t="s">
-        <v>108</v>
+        <v>125</v>
+      </c>
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
       </c>
       <c r="O19" t="s">
         <v>17</v>
@@ -2437,7 +2737,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -2446,31 +2746,37 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>128</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L20" t="s">
-        <v>113</v>
-      </c>
-      <c r="N20">
-        <v>3.2</v>
+        <v>130</v>
+      </c>
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>131</v>
       </c>
       <c r="O20" t="s">
         <v>17</v>
@@ -2481,7 +2787,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -2490,42 +2796,48 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" t="s">
         <v>115</v>
       </c>
-      <c r="E21" t="s">
-        <v>98</v>
-      </c>
       <c r="F21" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>117</v>
+        <v>135</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>61</v>
+        <v>71</v>
+      </c>
+      <c r="L21" t="s">
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>118</v>
-      </c>
-      <c r="N21">
-        <v>3.31</v>
+        <v>136</v>
+      </c>
+      <c r="N21" t="s">
+        <v>137</v>
       </c>
       <c r="O21" t="s">
         <v>17</v>
       </c>
       <c r="P21" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -2534,39 +2846,48 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
       <c r="K22" t="s">
-        <v>122</v>
+        <v>141</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
       </c>
       <c r="M22" t="s">
-        <v>118</v>
-      </c>
-      <c r="N22">
-        <v>3.31</v>
+        <v>136</v>
+      </c>
+      <c r="N22" t="s">
+        <v>137</v>
       </c>
       <c r="O22" t="s">
         <v>17</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -2575,34 +2896,37 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="J23" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K23" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s">
-        <v>128</v>
-      </c>
-      <c r="N23">
-        <v>2.28</v>
+        <v>147</v>
+      </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>90</v>
       </c>
       <c r="O23" t="s">
         <v>17</v>
@@ -2613,7 +2937,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -2622,34 +2946,37 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="J24" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="K24" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s">
-        <v>132</v>
-      </c>
-      <c r="N24">
-        <v>3.9</v>
+        <v>151</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>155</v>
       </c>
       <c r="O24" t="s">
         <v>17</v>
@@ -2660,7 +2987,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -2669,13 +2996,13 @@
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="G25" t="s">
         <v>21</v>
@@ -2684,16 +3011,22 @@
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="J25" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K25" t="s">
-        <v>141</v>
-      </c>
-      <c r="N25">
-        <v>3.2</v>
+        <v>161</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>131</v>
       </c>
       <c r="O25" t="s">
         <v>17</v>
@@ -2704,7 +3037,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -2713,31 +3046,37 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="J26" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K26" t="s">
-        <v>146</v>
+        <v>166</v>
+      </c>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" t="s">
+        <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
@@ -2748,7 +3087,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -2757,31 +3096,37 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E27" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="F27" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="J27" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K27" t="s">
-        <v>153</v>
+        <v>173</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" t="s">
+        <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="O27" t="s">
         <v>17</v>
@@ -2792,7 +3137,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -2801,31 +3146,37 @@
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>178</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s">
-        <v>160</v>
-      </c>
-      <c r="N28">
-        <v>1.6</v>
+        <v>180</v>
+      </c>
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>23</v>
       </c>
       <c r="O28" t="s">
         <v>17</v>
@@ -2836,7 +3187,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -2845,13 +3196,13 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="G29" t="s">
         <v>17</v>
@@ -2859,11 +3210,23 @@
       <c r="H29" t="s">
         <v>17</v>
       </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s">
+        <v>17</v>
+      </c>
       <c r="K29" t="s">
-        <v>165</v>
-      </c>
-      <c r="N29">
-        <v>3.47</v>
+        <v>184</v>
+      </c>
+      <c r="L29" t="s">
+        <v>185</v>
+      </c>
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>186</v>
       </c>
       <c r="O29" t="s">
         <v>17</v>
@@ -2874,7 +3237,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -2883,10 +3246,10 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
         <v>17</v>
@@ -2897,8 +3260,23 @@
       <c r="H30" t="s">
         <v>17</v>
       </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
       <c r="K30" t="s">
-        <v>169</v>
+        <v>189</v>
+      </c>
+      <c r="L30" t="s">
+        <v>185</v>
+      </c>
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
       </c>
       <c r="O30" t="s">
         <v>17</v>
@@ -2909,7 +3287,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2918,13 +3296,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="G31" t="s">
         <v>17</v>
@@ -2933,13 +3311,22 @@
         <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>174</v>
+        <v>193</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>175</v>
-      </c>
-      <c r="N31">
-        <v>3.47</v>
+        <v>194</v>
+      </c>
+      <c r="L31" t="s">
+        <v>185</v>
+      </c>
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>186</v>
       </c>
       <c r="O31" t="s">
         <v>17</v>
@@ -2950,7 +3337,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2959,10 +3346,10 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
@@ -2974,13 +3361,22 @@
         <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>179</v>
+        <v>197</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>180</v>
-      </c>
-      <c r="N32">
-        <v>3.47</v>
+        <v>198</v>
+      </c>
+      <c r="L32" t="s">
+        <v>185</v>
+      </c>
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>186</v>
       </c>
       <c r="O32" t="s">
         <v>17</v>
@@ -2991,7 +3387,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -3000,10 +3396,10 @@
         <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
         <v>17</v>
@@ -3015,16 +3411,22 @@
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="J33" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K33" t="s">
-        <v>186</v>
-      </c>
-      <c r="N33">
-        <v>3.77</v>
+        <v>203</v>
+      </c>
+      <c r="L33" t="s">
+        <v>204</v>
+      </c>
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>205</v>
       </c>
       <c r="O33" t="s">
         <v>17</v>
@@ -3035,7 +3437,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -3044,10 +3446,10 @@
         <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="E34" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
@@ -3059,13 +3461,22 @@
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>179</v>
+        <v>197</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>190</v>
-      </c>
-      <c r="N34">
-        <v>3.47</v>
+        <v>208</v>
+      </c>
+      <c r="L34" t="s">
+        <v>185</v>
+      </c>
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>186</v>
       </c>
       <c r="O34" t="s">
         <v>17</v>
@@ -3076,7 +3487,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -3085,10 +3496,10 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
@@ -3100,13 +3511,22 @@
         <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="J35" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K35" t="s">
-        <v>195</v>
+        <v>212</v>
+      </c>
+      <c r="L35" t="s">
+        <v>131</v>
+      </c>
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>17</v>
       </c>
       <c r="O35" t="s">
         <v>17</v>
@@ -3117,7 +3537,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -3126,13 +3546,13 @@
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
@@ -3141,19 +3561,22 @@
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="J36" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="K36" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="L36" t="s">
-        <v>200</v>
-      </c>
-      <c r="N36">
-        <v>1.98</v>
+        <v>217</v>
+      </c>
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>44</v>
       </c>
       <c r="O36" t="s">
         <v>17</v>
@@ -3164,7 +3587,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -3173,13 +3596,13 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s">
         <v>19</v>
@@ -3188,19 +3611,22 @@
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="J37" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="K37" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s">
-        <v>204</v>
-      </c>
-      <c r="N37">
-        <v>2.33</v>
+        <v>221</v>
+      </c>
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>80</v>
       </c>
       <c r="O37" t="s">
         <v>17</v>
@@ -3211,7 +3637,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -3220,20 +3646,38 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
       <c r="O38" t="s">
         <v>17</v>
       </c>
@@ -3241,9 +3685,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -3252,31 +3696,37 @@
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F39" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="J39" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="K39" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="L39" t="s">
-        <v>215</v>
+        <v>232</v>
+      </c>
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>17</v>
       </c>
       <c r="O39" t="s">
         <v>17</v>
@@ -3287,7 +3737,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -3296,28 +3746,37 @@
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F40" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G40" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="K40" t="s">
-        <v>122</v>
+        <v>141</v>
+      </c>
+      <c r="L40" t="s">
+        <v>17</v>
+      </c>
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>17</v>
       </c>
       <c r="O40" t="s">
         <v>17</v>
@@ -3328,7 +3787,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -3337,18 +3796,36 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
         <v>17</v>
       </c>
       <c r="O41" t="s">
@@ -3375,16 +3852,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B1" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="C1" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3404,21 +3881,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="B1" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="C1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D1" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>328</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3427,12 +3904,12 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>330</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3441,12 +3918,12 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>282</v>
+        <v>332</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3455,12 +3932,12 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3469,12 +3946,12 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3483,12 +3960,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3497,12 +3974,12 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3511,12 +3988,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3525,12 +4002,12 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3539,12 +4016,12 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3553,12 +4030,12 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3567,12 +4044,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3581,12 +4058,12 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3595,12 +4072,12 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3609,12 +4086,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3623,12 +4100,12 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3637,12 +4114,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3651,12 +4128,12 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3665,12 +4142,12 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3679,12 +4156,12 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3693,12 +4170,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>369</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3707,12 +4184,12 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3721,12 +4198,12 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3735,12 +4212,12 @@
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3749,12 +4226,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3763,12 +4240,12 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3777,12 +4254,12 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3791,12 +4268,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3805,12 +4282,12 @@
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3819,12 +4296,12 @@
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3833,12 +4310,12 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3847,12 +4324,12 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3861,12 +4338,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3875,12 +4352,12 @@
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>345</v>
+        <v>395</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3889,12 +4366,12 @@
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>347</v>
+        <v>397</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3903,12 +4380,12 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3917,12 +4394,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3931,12 +4408,12 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3945,12 +4422,12 @@
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3959,12 +4436,12 @@
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3973,12 +4450,12 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>359</v>
+        <v>409</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3987,12 +4464,12 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>361</v>
+        <v>411</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4001,12 +4478,12 @@
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>363</v>
+        <v>413</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4015,12 +4492,12 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>365</v>
+        <v>415</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4029,12 +4506,12 @@
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4043,12 +4520,12 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4057,12 +4534,12 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>371</v>
+        <v>421</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4071,12 +4548,12 @@
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>373</v>
+        <v>423</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4085,12 +4562,12 @@
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4099,12 +4576,12 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4113,12 +4590,12 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4127,12 +4604,12 @@
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4141,12 +4618,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4155,12 +4632,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -4169,12 +4646,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4183,12 +4660,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -4197,12 +4674,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -4211,12 +4688,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -4225,12 +4702,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -4239,12 +4716,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -4253,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4347,7 +4824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="0" outlineLevelCol="4" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4362,27 +4839,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="E1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -4390,16 +4867,19 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -4407,16 +4887,19 @@
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -4424,16 +4907,19 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -4441,33 +4927,39 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -4475,16 +4967,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -4492,16 +4987,19 @@
       <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>255</v>
       </c>
       <c r="C9" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -4509,16 +5007,19 @@
       <c r="E9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4526,16 +5027,19 @@
       <c r="E10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -4543,16 +5047,19 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -4560,16 +5067,19 @@
       <c r="E12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -4577,16 +5087,19 @@
       <c r="E13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>265</v>
       </c>
       <c r="C14" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -4594,33 +5107,39 @@
       <c r="E14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" t="s">
         <v>244</v>
       </c>
-      <c r="B15" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" t="s">
-        <v>231</v>
-      </c>
       <c r="D15" t="s">
         <v>17</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -4628,16 +5147,19 @@
       <c r="E16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -4645,16 +5167,19 @@
       <c r="E17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -4662,22 +5187,88 @@
       <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
       </c>
       <c r="E19">
         <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>275</v>
+      </c>
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>276</v>
+      </c>
+      <c r="B21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>277</v>
+      </c>
+      <c r="B22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4800,39 +5391,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="B1" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="D1" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="E1" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="F1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
@@ -4840,19 +5431,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="E3" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -4860,19 +5451,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
@@ -4880,19 +5471,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="E5" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -4928,22 +5519,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B1" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="D1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="E1" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="F1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -4963,27 +5554,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B1" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>305</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -5006,24 +5597,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="B1" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="C1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D1" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5032,15 +5623,15 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5049,15 +5640,15 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5066,15 +5657,15 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5083,15 +5674,15 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5100,15 +5691,15 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>312</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -5117,15 +5708,15 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -5134,15 +5725,15 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5151,15 +5742,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>315</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -5168,15 +5759,15 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>316</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>317</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -5185,15 +5776,15 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C12">
         <v>26</v>
@@ -5202,15 +5793,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -5219,15 +5810,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -5236,15 +5827,15 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>319</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>320</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -5253,15 +5844,15 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>321</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5270,15 +5861,15 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>322</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>323</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5287,15 +5878,15 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>249</v>
+        <v>324</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -5304,15 +5895,15 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -5321,7 +5912,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -5346,24 +5937,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C1" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="D1" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="E1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>328</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -5377,10 +5968,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>331</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -5394,10 +5985,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>282</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>333</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -5411,10 +6002,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5428,10 +6019,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -5445,10 +6036,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -5462,10 +6053,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -5479,10 +6070,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -5496,10 +6087,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -5513,10 +6104,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="B11" t="s">
-        <v>297</v>
+        <v>347</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -5530,10 +6121,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -5547,10 +6138,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -5564,16 +6155,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="B14" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5581,10 +6172,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="B15" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -5598,10 +6189,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="B16" t="s">
-        <v>308</v>
+        <v>358</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -5615,10 +6206,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -5632,10 +6223,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -5649,10 +6240,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="B19" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
@@ -5666,10 +6257,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
@@ -5683,10 +6274,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="B21" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -5700,10 +6291,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>369</v>
       </c>
       <c r="B22" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -5717,10 +6308,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
       <c r="B23" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -5734,10 +6325,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="B24" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -5751,10 +6342,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="B25" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -5768,10 +6359,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="B26" t="s">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -5785,10 +6376,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="B27" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -5802,10 +6393,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="B28" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -5819,10 +6410,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="B29" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -5836,10 +6427,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="B30" t="s">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -5853,10 +6444,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="B31" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
@@ -5870,10 +6461,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="B32" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -5887,10 +6478,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="B33" t="s">
-        <v>342</v>
+        <v>392</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
@@ -5904,10 +6495,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="B34" t="s">
-        <v>344</v>
+        <v>394</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
@@ -5921,10 +6512,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>345</v>
+        <v>395</v>
       </c>
       <c r="B35" t="s">
-        <v>346</v>
+        <v>396</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
@@ -5938,10 +6529,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>347</v>
+        <v>397</v>
       </c>
       <c r="B36" t="s">
-        <v>348</v>
+        <v>398</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
@@ -5955,10 +6546,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="B37" t="s">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -5972,10 +6563,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>352</v>
+        <v>402</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -5989,10 +6580,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s">
-        <v>354</v>
+        <v>404</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -6006,10 +6597,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s">
-        <v>356</v>
+        <v>406</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -6023,10 +6614,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s">
-        <v>358</v>
+        <v>408</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -6040,10 +6631,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>359</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -6057,10 +6648,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>361</v>
+        <v>411</v>
       </c>
       <c r="B43" t="s">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -6074,10 +6665,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>363</v>
+        <v>413</v>
       </c>
       <c r="B44" t="s">
-        <v>364</v>
+        <v>414</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
@@ -6091,10 +6682,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>365</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s">
-        <v>366</v>
+        <v>416</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
@@ -6108,10 +6699,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s">
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
@@ -6125,10 +6716,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s">
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
@@ -6142,10 +6733,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>371</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s">
-        <v>372</v>
+        <v>422</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
@@ -6159,10 +6750,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>373</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
@@ -6176,10 +6767,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
@@ -6193,10 +6784,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>428</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
@@ -6210,10 +6801,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="B52" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
@@ -6227,10 +6818,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
@@ -6244,10 +6835,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
@@ -6261,10 +6852,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
@@ -6278,10 +6869,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
@@ -6295,10 +6886,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
@@ -6312,10 +6903,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
@@ -6329,10 +6920,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
@@ -6346,10 +6937,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="B60" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
@@ -6363,10 +6954,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
@@ -6398,22 +6989,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="B1" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="C1" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="D1" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="E1" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="F1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -6436,27 +7027,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B1" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="C1" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="D1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="E1" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="F1" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -6468,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
